--- a/Diện tích nhà ở bình quân đầu người phân theo loại nhà và phân theo địa phương chia theo Địa phương, Năm và Loại nhà.xlsx
+++ b/Diện tích nhà ở bình quân đầu người phân theo loại nhà và phân theo địa phương chia theo Địa phương, Năm và Loại nhà.xlsx
@@ -1450,16 +1450,16 @@
       <c r="B1" s="1">
         <v>2014.0</v>
       </c>
-      <c r="C1" s="1">
+      <c r="G1" s="1">
         <v>2016.0</v>
       </c>
-      <c r="D1" s="1">
+      <c r="L1" s="1">
         <v>2018.0</v>
       </c>
-      <c r="E1" s="1">
+      <c r="Q1" s="1">
         <v>2020.0</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
